--- a/excel/Batch_08_Leads_Tracker.xlsx
+++ b/excel/Batch_08_Leads_Tracker.xlsx
@@ -532,10 +532,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L2" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M2" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N2" t="str">
         <v>Final follow-up — Masta Plumbing &amp; Heating website concept</v>
@@ -616,10 +616,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L3" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M3" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N3" t="str">
         <v>Final follow-up — Acorn Heating and Plumbing website concept</v>
@@ -700,10 +700,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L4" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M4" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N4" t="str">
         <v>Final follow-up — SW Locksmith website concept</v>
@@ -784,10 +784,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L5" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M5" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N5" t="str">
         <v>Final follow-up — RN Locksmiths website concept</v>
@@ -826,8 +826,8 @@
         <v>01622 843284 / 07712 801308</v>
       </c>
       <c r="E6" t="str" xml:space="preserve">
-        <v xml:space="preserve">Facebook
-Instagram</v>
+        <v xml:space="preserve">Facebook: Facebook
+Instagram: Instagram</v>
       </c>
       <c r="F6" t="str">
         <v>A homepage redesign concept for Peter Fournel Antique Restoration &amp; Upholstery</v>
@@ -869,10 +869,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L6" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M6" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N6" t="str">
         <v>Final follow-up — Peter Fournel Antique Restoration &amp; Upholstery website concept</v>
@@ -911,9 +911,9 @@
         <v>020 7372 4092 / 07940 508530</v>
       </c>
       <c r="E7" t="str" xml:space="preserve">
-        <v xml:space="preserve">Facebook
-Instagram
-LinkedIn</v>
+        <v xml:space="preserve">Facebook: Facebook
+Instagram: Instagram
+LinkedIn: LinkedIn</v>
       </c>
       <c r="F7" t="str">
         <v>A homepage redesign concept for The Painting Specialist</v>
@@ -955,10 +955,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L7" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M7" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N7" t="str">
         <v>Final follow-up — The Painting Specialist website concept</v>
@@ -1039,10 +1039,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L8" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M8" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N8" t="str">
         <v>Final follow-up — Upholster London website concept</v>
@@ -1081,8 +1081,8 @@
         <v>020 3592 7953</v>
       </c>
       <c r="E9" t="str" xml:space="preserve">
-        <v xml:space="preserve">Facebook
-Instagram</v>
+        <v xml:space="preserve">Facebook: Facebook
+Instagram: Instagram</v>
       </c>
       <c r="F9" t="str">
         <v>A homepage redesign concept for Industry Decorators</v>
@@ -1124,10 +1124,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L9" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M9" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N9" t="str">
         <v>Final follow-up — Industry Decorators website concept</v>
@@ -1208,10 +1208,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L10" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M10" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N10" t="str">
         <v>Final follow-up — Holton Building Services website concept</v>
@@ -1250,7 +1250,7 @@
         <v>0203 129 4247</v>
       </c>
       <c r="E11" t="str">
-        <v>Facebook</v>
+        <v>Facebook: Facebook</v>
       </c>
       <c r="F11" t="str">
         <v>A homepage redesign concept for London Clean Carpet</v>
@@ -1292,10 +1292,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L11" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M11" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N11" t="str">
         <v>Final follow-up — London Clean Carpet website concept</v>
@@ -1376,10 +1376,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L12" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M12" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N12" t="str">
         <v>Final follow-up — London Carpet Cleaner website concept</v>
@@ -1412,7 +1412,7 @@
         <v>https://unlimitedcarpetclean.com/</v>
       </c>
       <c r="C13" t="str">
-        <v>Not found</v>
+        <v>info@unlimitedcarpetclean.com</v>
       </c>
       <c r="D13" t="str">
         <v>07727 979607 / 0208 257 8024</v>
@@ -1460,10 +1460,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L13" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M13" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N13" t="str">
         <v>Final follow-up — Unlimited Carpet Clean website concept</v>
@@ -1544,10 +1544,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L14" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M14" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N14" t="str">
         <v>Final follow-up — Furniture Restorers in London website concept</v>
@@ -1628,10 +1628,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L15" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M15" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N15" t="str">
         <v>Final follow-up — Barrdale French Polishers website concept</v>
@@ -1712,10 +1712,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L16" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M16" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N16" t="str">
         <v>Final follow-up — Coffee Matters London website concept</v>
@@ -1796,10 +1796,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L17" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M17" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N17" t="str">
         <v>Final follow-up — London Interior Blinds website concept</v>
@@ -1880,10 +1880,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L18" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M18" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N18" t="str">
         <v>Final follow-up — Hatton Garden Workshop website concept</v>
@@ -1965,10 +1965,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L19" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M19" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N19" t="str">
         <v>Final follow-up — No One Famous Tailoring website concept</v>
@@ -2049,10 +2049,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L20" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M20" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N20" t="str">
         <v>Final follow-up — OIS Removals website concept</v>
@@ -2091,10 +2091,10 @@
         <v>020 8866 3413</v>
       </c>
       <c r="E21" t="str" xml:space="preserve">
-        <v xml:space="preserve">Facebook
-Instagram
-LinkedIn
-YouTube</v>
+        <v xml:space="preserve">Facebook: Facebook
+Instagram: Instagram
+LinkedIn: LinkedIn
+YouTube: YouTube</v>
       </c>
       <c r="F21" t="str">
         <v>A homepage redesign concept for J&amp;I Cleaning Services</v>
@@ -2136,10 +2136,10 @@
 The redesign can be kept affordable, usually around $200 to $800 depending on what you need. You do not need to pay anything upfront. Payment is only after the website is delivered and you are happy with the result.</v>
       </c>
       <c r="L21" t="str">
-        <v>Draft</v>
+        <v>Sent</v>
       </c>
       <c r="M21" t="str">
-        <v/>
+        <v>2026-09-22</v>
       </c>
       <c r="N21" t="str">
         <v>Final follow-up — J&amp;I Cleaning Services website concept</v>
